--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
@@ -73,6 +73,36 @@
   </x:si>
   <x:si>
     <x:t>1129</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Values</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total Sum Amount paid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total Sum Items total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum Amount paid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum Items total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Credit Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MC Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Visa Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Action Club Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Total</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -319,7 +349,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="8">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -338,6 +368,60 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="15" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -1223,8 +1307,232 @@
     <x:col min="6" max="6" width="13.832031" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="4" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <x:row r="14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <x:row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B3" s="13"/>
+      <x:c r="C3" s="14"/>
+      <x:c r="D3" s="14"/>
+      <x:c r="E3" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G3" s="14"/>
+      <x:c r="H3" s="17"/>
+    </x:row>
+    <x:row r="4" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <x:c r="B4" s="18"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="39">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="38"/>
+      <x:c r="G4" s="32" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H4" s="41" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B5" s="13" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="32" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F5" s="42" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G5" s="18"/>
+      <x:c r="H5" s="40"/>
+    </x:row>
+    <x:row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B6" s="32" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E6" s="19">
+        <x:v>134.85</x:v>
+      </x:c>
+      <x:c r="F6" s="20">
+        <x:v>134.85</x:v>
+      </x:c>
+      <x:c r="G6" s="19">
+        <x:v>134.85</x:v>
+      </x:c>
+      <x:c r="H6" s="21">
+        <x:v>134.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B7" s="18"/>
+      <x:c r="C7" s="32" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D7" s="14"/>
+      <x:c r="E7" s="19">
+        <x:v>134.85</x:v>
+      </x:c>
+      <x:c r="F7" s="20">
+        <x:v>134.85</x:v>
+      </x:c>
+      <x:c r="G7" s="19">
+        <x:v>134.85</x:v>
+      </x:c>
+      <x:c r="H7" s="21">
+        <x:v>134.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B8" s="18"/>
+      <x:c r="C8" s="32" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E8" s="19">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="F8" s="20">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="G8" s="19">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="H8" s="21">
+        <x:v>20108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B9" s="18"/>
+      <x:c r="C9" s="18"/>
+      <x:c r="D9" s="37" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E9" s="22">
+        <x:v>1004.8</x:v>
+      </x:c>
+      <x:c r="F9" s="0">
+        <x:v>1004.8</x:v>
+      </x:c>
+      <x:c r="G9" s="22">
+        <x:v>1004.8</x:v>
+      </x:c>
+      <x:c r="H9" s="24">
+        <x:v>1004.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B10" s="18"/>
+      <x:c r="C10" s="32" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="14"/>
+      <x:c r="E10" s="19">
+        <x:v>21112.8</x:v>
+      </x:c>
+      <x:c r="F10" s="20">
+        <x:v>21112.8</x:v>
+      </x:c>
+      <x:c r="G10" s="19">
+        <x:v>21112.8</x:v>
+      </x:c>
+      <x:c r="H10" s="21">
+        <x:v>21112.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B11" s="18"/>
+      <x:c r="C11" s="32" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E11" s="19">
+        <x:v>10152</x:v>
+      </x:c>
+      <x:c r="F11" s="20">
+        <x:v>10152</x:v>
+      </x:c>
+      <x:c r="G11" s="19">
+        <x:v>10152</x:v>
+      </x:c>
+      <x:c r="H11" s="21">
+        <x:v>10152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B12" s="18"/>
+      <x:c r="C12" s="32" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D12" s="14"/>
+      <x:c r="E12" s="19">
+        <x:v>10152</x:v>
+      </x:c>
+      <x:c r="F12" s="20">
+        <x:v>10152</x:v>
+      </x:c>
+      <x:c r="G12" s="19">
+        <x:v>10152</x:v>
+      </x:c>
+      <x:c r="H12" s="21">
+        <x:v>10152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <x:c r="B13" s="32" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="14"/>
+      <x:c r="D13" s="14"/>
+      <x:c r="E13" s="28">
+        <x:v>31399.65</x:v>
+      </x:c>
+      <x:c r="F13" s="29">
+        <x:v>31399.65</x:v>
+      </x:c>
+      <x:c r="G13" s="28">
+        <x:v>31399.65</x:v>
+      </x:c>
+      <x:c r="H13" s="30">
+        <x:v>31399.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <x:c r="B14" s="35" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="34"/>
+      <x:c r="D14" s="34"/>
+      <x:c r="E14" s="25">
+        <x:v>31399.65</x:v>
+      </x:c>
+      <x:c r="F14" s="26">
+        <x:v>31399.65</x:v>
+      </x:c>
+      <x:c r="G14" s="25">
+        <x:v>31399.65</x:v>
+      </x:c>
+      <x:c r="H14" s="27">
+        <x:v>31399.65</x:v>
+      </x:c>
+    </x:row>
     <x:row r="29" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <x:row r="30" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <x:row r="42" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1302,6 +1610,18 @@
     <x:row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <x:row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </x:sheetData>
+  <x:mergeCells count="10">
+    <x:mergeCell ref="E4:F4"/>
+    <x:mergeCell ref="G4:G5"/>
+    <x:mergeCell ref="H4:H5"/>
+    <x:mergeCell ref="B6:B12"/>
+    <x:mergeCell ref="C7:D7"/>
+    <x:mergeCell ref="C8:C9"/>
+    <x:mergeCell ref="C10:D10"/>
+    <x:mergeCell ref="C12:D12"/>
+    <x:mergeCell ref="B13:D13"/>
+    <x:mergeCell ref="B14:D14"/>
+  </x:mergeCells>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
@@ -662,7 +662,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" mergeItem="1" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataPosition="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" mergeItem="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="B3:H14" firstHeaderRow="1" firstDataRow="3" firstDataCol="3"/>
   <pivotFields count="7">
     <pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1">
